--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +117,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -226,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -288,19 +294,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,7 +1221,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1222,12 +1231,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1237,12 +1246,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1252,7 +1261,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1291,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1292,12 +1301,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1307,12 +1316,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1322,7 +1331,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1501,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1502,12 +1511,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1517,12 +1526,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1532,7 +1541,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1571,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1572,12 +1581,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1587,12 +1596,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1602,7 +1611,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1921,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1922,12 +1931,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1937,12 +1946,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1952,7 +1961,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1991,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1992,12 +2001,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2007,12 +2016,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2022,7 +2031,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2901,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2902,12 +2911,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2917,12 +2926,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2971,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2972,12 +2981,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2987,12 +2996,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3002,7 +3011,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3181,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3182,12 +3191,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -3197,12 +3206,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3212,7 +3221,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3251,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3252,12 +3261,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3267,12 +3276,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3282,7 +3291,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4056,27 +4065,27 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -4181,20 +4190,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4227,20 +4236,20 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4296,20 +4305,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4429,27 +4438,27 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -4577,20 +4586,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4623,20 +4632,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4795,32 +4804,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>

--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="24">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +119,11 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -232,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -244,6 +251,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,22 +304,25 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,8 +699,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -1291,23 +1304,19 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>48831000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36937</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1316,12 +1325,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1331,7 +1340,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4019,100 +4028,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>住宅大楼 - 东翼 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 2217呎 (4+房)
 -
@@ -4120,15 +4129,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 2207呎 (3房)
 -
@@ -4136,15 +4145,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4152,7 +4161,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4162,12 +4171,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (3房)
 -
@@ -4175,7 +4184,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4185,12 +4194,58 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+$4883万
+$36,937/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -4198,7 +4253,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4207,13 +4262,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4221,7 +4276,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4230,13 +4285,36 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -4244,7 +4322,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4253,13 +4331,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4267,7 +4345,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4276,13 +4354,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4290,76 +4368,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4392,100 +4401,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>住宅大楼 - 西翼 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 2217呎 (4+房)
 -
@@ -4493,15 +4502,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 2207呎 (4+房)
 -
@@ -4509,15 +4518,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4525,7 +4534,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4535,12 +4544,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4548,7 +4557,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4558,12 +4567,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4571,7 +4580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4581,12 +4590,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -4594,7 +4603,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4604,12 +4613,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4617,7 +4626,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4627,12 +4636,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -4640,7 +4649,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4650,12 +4659,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4663,7 +4672,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4673,12 +4682,12 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4686,7 +4695,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4696,12 +4705,12 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4709,7 +4718,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4719,12 +4728,12 @@
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4732,7 +4741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4772,64 +4781,64 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
@@ -4858,7 +4867,7 @@
           <t>独立屋</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>1号屋
 2623呎 (4+房)
@@ -4867,7 +4876,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>2号屋
 2621呎 (4+房)

--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 东翼" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
-  <fonts count="25">
+  <numFmts count="0"/>
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,11 +116,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -239,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -251,9 +243,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -304,25 +293,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -699,8 +685,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -791,7 +777,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -861,7 +847,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -931,7 +917,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1001,7 +987,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1071,7 +1057,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1141,7 +1127,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1156,7 +1142,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1211,7 +1197,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1234,7 +1220,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1244,12 +1230,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1259,12 +1245,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1274,14 +1260,14 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1304,19 +1290,23 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>48831000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>36937</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1347,7 +1337,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1370,7 +1360,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1380,12 +1370,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1395,12 +1385,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1410,14 +1400,14 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1440,7 +1430,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1450,12 +1440,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1465,12 +1455,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1480,14 +1470,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1510,7 +1500,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1520,12 +1510,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1535,12 +1525,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1550,14 +1540,14 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1580,7 +1570,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1590,12 +1580,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1605,12 +1595,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1620,14 +1610,14 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1650,7 +1640,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1660,12 +1650,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1675,12 +1665,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1690,14 +1680,14 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1720,7 +1710,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1730,12 +1720,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1745,12 +1735,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1760,14 +1750,14 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1837,7 +1827,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1907,7 +1897,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1930,7 +1920,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1940,12 +1930,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1955,12 +1945,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1970,14 +1960,14 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2000,7 +1990,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2010,12 +2000,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2025,12 +2015,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2040,14 +2030,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2117,7 +2107,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2187,7 +2177,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2257,7 +2247,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 东翼</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2327,17 +2317,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>1号屋</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2346,7 +2336,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2217</v>
+        <v>2623</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2397,17 +2387,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>2号屋</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2416,7 +2406,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2207</v>
+        <v>2621</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2459,1546 +2449,6 @@
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>1号屋</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>2623</v>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>2号屋</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>2621</v>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -4028,100 +2478,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 东翼 销控网格图</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>A | 2217呎 (4+房)
 -
@@ -4129,31 +2579,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2207呎 (3房)
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>A | 2207呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4161,7 +2611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4171,20 +2621,20 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (3房)
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4194,20 +2644,43 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
-$4883万
-$36,937/呎
-(26年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4216,13 +2689,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4230,7 +2703,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4239,13 +2712,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -4253,7 +2726,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -4262,13 +2735,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4276,7 +2749,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4285,13 +2758,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4299,7 +2772,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4308,36 +2781,36 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -4345,30 +2818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -4392,379 +2842,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 2217呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2207呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4781,64 +2858,64 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
@@ -4867,7 +2944,7 @@
           <t>独立屋</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>1号屋
 2623呎 (4+房)
@@ -4876,7 +2953,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2号屋
 2621呎 (4+房)

--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 东翼" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="24">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +119,11 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -231,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -243,6 +251,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -293,22 +304,25 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -676,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -685,8 +699,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -777,7 +791,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -847,7 +861,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -862,7 +876,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -917,7 +931,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -987,7 +1001,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1057,7 +1071,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1127,7 +1141,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1142,7 +1156,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1197,7 +1211,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1220,7 +1234,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1230,12 +1244,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1245,12 +1259,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1260,14 +1274,14 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1290,23 +1304,19 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>48831000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36937</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1337,7 +1347,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1360,7 +1370,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1370,12 +1380,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1385,12 +1395,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1400,14 +1410,14 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1430,7 +1440,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1440,12 +1450,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1455,12 +1465,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1470,14 +1480,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1500,7 +1510,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1510,12 +1520,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1525,12 +1535,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1540,14 +1550,14 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1570,7 +1580,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1580,12 +1590,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1595,12 +1605,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1610,14 +1620,14 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1640,7 +1650,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1650,12 +1660,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1665,12 +1675,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1680,14 +1690,14 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1710,7 +1720,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1720,12 +1730,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1735,12 +1745,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1750,14 +1760,14 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1827,7 +1837,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1897,7 +1907,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1920,7 +1930,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1930,12 +1940,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1945,12 +1955,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1960,14 +1970,14 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1990,7 +2000,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2000,12 +2010,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2015,12 +2025,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2030,14 +2040,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2107,7 +2117,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2177,7 +2187,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2247,7 +2257,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>住宅大楼 - 西翼</t>
+          <t>住宅大楼 - 东翼</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2317,17 +2327,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>1号屋</t>
+          <t>住宅大楼 - 西翼</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2336,7 +2346,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2623</v>
+        <v>2217</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2387,68 +2397,1608 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>2207</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>2623</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>2号屋</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>2621</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2478,100 +4028,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>住宅大楼 - 西翼 销控网格图</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 东翼 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 2217呎 (4+房)
 -
@@ -2579,31 +4129,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A | 2207呎 (4+房)
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2207呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -2611,7 +4161,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -2621,20 +4171,66 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
+$4883万
+$36,937/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -2643,36 +4239,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -2680,7 +4253,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -2689,13 +4262,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -2703,7 +4276,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -2712,13 +4285,36 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 招标单位
@@ -2726,7 +4322,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 招标单位
@@ -2735,13 +4331,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -2749,7 +4345,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -2758,13 +4354,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1322呎 (4+房)
 -
@@ -2772,53 +4368,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1089呎 (3房)
 -
@@ -2842,6 +4392,379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2217呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2207呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2858,64 +4781,64 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>2 套</t>
         </is>
@@ -2944,7 +4867,7 @@
           <t>独立屋</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>1号屋
 2623呎 (4+房)
@@ -2953,7 +4876,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>2号屋
 2621呎 (4+房)

--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -4204,7 +4204,7 @@
           <t>A | 1322呎 (4+房)
 $4883万
 $36,937/呎
-(26年-09月-30日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
